--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/MASSACHUSETTS_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/MASSACHUSETTS_2018.xlsx
@@ -1579,7 +1579,7 @@
         <v>6</v>
       </c>
       <c r="D68">
-        <v>0.009538950715421303</v>
+        <v>0.009538950715421305</v>
       </c>
     </row>
     <row r="69">
@@ -1741,7 +1741,7 @@
         <v>6</v>
       </c>
       <c r="D77">
-        <v>0.009538950715421303</v>
+        <v>0.009538950715421305</v>
       </c>
     </row>
     <row r="78">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C79">
@@ -4441,7 +4441,7 @@
         <v>6</v>
       </c>
       <c r="D227">
-        <v>0.009538950715421303</v>
+        <v>0.009538950715421305</v>
       </c>
     </row>
     <row r="228">
